--- a/NGS_comments_automation_further_review.xlsx
+++ b/NGS_comments_automation_further_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCC3220-21AD-4932-A6A8-E8074E5E797B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677BE400-22EC-44C8-8652-40C40ED94734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29835" yWindow="-450" windowWidth="24840" windowHeight="14985" firstSheet="14" activeTab="21" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="30570" yWindow="-1080" windowWidth="25980" windowHeight="14790" firstSheet="13" activeTab="20" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,8 @@
     <sheet name="Histiocytic disorders" sheetId="16" r:id="rId17"/>
     <sheet name="Caveats" sheetId="11" r:id="rId18"/>
     <sheet name="Panel" sheetId="12" r:id="rId19"/>
-    <sheet name="CNV" sheetId="13" r:id="rId20"/>
-    <sheet name="CLL CNV detected" sheetId="26" r:id="rId21"/>
-    <sheet name="CLL CNV" sheetId="27" r:id="rId22"/>
+    <sheet name="CNV lymphoid" sheetId="13" r:id="rId20"/>
+    <sheet name="CLL CNV" sheetId="27" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +81,7 @@
     <author>tc={61FD660D-2DBF-40EC-B926-88247D8CDA05}</author>
   </authors>
   <commentList>
-    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -95,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="523">
   <si>
     <t>Gene</t>
   </si>
@@ -136,9 +135,6 @@
     <t>Genes</t>
   </si>
   <si>
-    <t>CLL</t>
-  </si>
-  <si>
     <t>Caveat</t>
   </si>
   <si>
@@ -232,29 +228,6 @@
     <t>Trisomy 19</t>
   </si>
   <si>
-    <t>Del(17p) occurs in 4 to 8% of early stage CLL, 5 to 8% at the start of first-line therapy, and 40–50% in relapsed/refractory CLL.
-Del(17p) and/or TP53 mutation have the strongest impact on the prognosis and the prediction of therapeutic outcome in CLL. They are associated with significantly worse progression-free survival (PFS) and overall survival (OS), both without treatment and with chemoimmunotherapy (CIT). However, their negative impact is less pronounced with targeted therapies like BTK and BCL2 inhibitors, which offer longer response durations and improved PFS and OS compared to CIT (WHO 5th ed.).
-The prognostic impact of single hit TP53 abnormalities (e.g., isolated del(17p) or TP53 mutation) with targeted therapies is currently unclear. Conversely, multi-hit TP53 aberrations (concomitant TP53 mutation and del(17p)) consistently correlates with poorer outcomes. (ERIC, 2024).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trisomy 12 occurs in 15 to 20% of CLL patients (WHO 5th edition). </t>
-  </si>
-  <si>
-    <t>Del(11q), has been detected in 10 to 20% of CLL patients, and removes the ATM gene (WHO 5th edition).</t>
-  </si>
-  <si>
-    <t>CNV analysis detected multiple copy number gains and/or copy number losses, suggestive of genomic complexity. Genomic complexity is an independent negative prognostic marker in CLL, particularly for ≥ 5 copy number aberrations in TP53 wildtype cases (WHO 5th ed, ERIC 2022).</t>
-  </si>
-  <si>
-    <t>Approximately 10% of CLL cases with trisomy 12 also have trisomy 19 and are associated with mutated IGHV genes in CLL  (PMID: 17593029)</t>
-  </si>
-  <si>
-    <t>No copy number aberrations detected in a sample with &gt;=40% NCC</t>
-  </si>
-  <si>
-    <t>No copy number aberrations detected in a sample with &lt;40% NCC</t>
-  </si>
-  <si>
     <t>CNV quality flag (assay noise score &gt;0.02)</t>
   </si>
   <si>
@@ -265,12 +238,6 @@
   </si>
   <si>
     <t>CNV detected (other) that doesn't reach threshold</t>
-  </si>
-  <si>
-    <t>CLL &lt;10% infiltration, no FISH activation</t>
-  </si>
-  <si>
-    <t>As the percentage neoplastic cell content in this sample is &lt;40% by immunophenotyping we cannot exclude the presence of copy number variants. Targeted FISH testing for TP53/ATM has been activated.</t>
   </si>
   <si>
     <t>It was not possible to perform CNV analysis for this sample, due to significant assay noise. Targeted FISH testing for TP53/ATM has been activated.</t>
@@ -526,17 +493,6 @@
     <t>PRPF8 mutations or deletions (within del(17p)) have been reported in AML (DOI: 10.1038/leu.2014.144).</t>
   </si>
   <si>
-    <t xml:space="preserve">Mutations in MDS related genes (ASXL1, BCOR, EZH2, RUNX1, SF3B1, SRSF2, STAG2, U2AF1, ZRSR2), together with MDS related cytogenetic abnormalities or a prior history of MDS or MDS/MPN, are used to classify cases as AML, myelodysplasia-related (AML-MR), in the absence of AML-defining recurrent genetic abnormalities. These mutations are associated with an adverse prognosis, including in de novo AML (WHO 5th Edition; ELN 2022).
-Note, not for reporting: AML-MR comment should only be used in the absence of AML-defining recurrent genetic abnormalities and mutated TP53 &gt;10%: PML::RARA, RUNX1::RUNX1T1, CBFB::MYH11, MLLT3::KMT2A, DEK::NUP214, inv(3) or t(3;3)/GATA2, MECOM(EVI1); mutated NPM1, in-frame bZIP mutated CEBPA, BCR::ABL1. 
-If biallelic add: 
-Sporadic AML with somatic RUNX1 mutations are associated with an adverse prognosis, and biallelic RUNX1 mutations have been linked to an even poorer outcome (DOI: 10.1182/bloodadvances.2019000901).
-Concurrent RUNX1 mutations have been reported in AML with KMT2A rearrangement and MECOM rearrangement.
-If suspected germline: 
-Germline RUNX1 mutated AML is encompassed by the WHO 5th Edition disease category of Myeloid neoplasms with germline predisposition and pre-existing platelet disorders. Heterozygous deleterious variants confer lifelong thrombocytopenia with variable degrees of platelet dysfunction and risk for myeloid malignancies (also referred to as familial platelet disorder). 
-AML patients with germline RUNX1 mutations have shown enrichment for somatic mutations affecting the second RUNX1 allele and GATA2 (DOI: 10.1182/bloodadvances.2019000901).
-Please note that this assay cannot exclude the germline origin for the RUNX1 c.xxx p.(xxx) variant. Identification of a germline predisposition may have implications for patient management including donor selection for allogeneic transplantation. Referral to clinical genetics service for family history and further assessment is recommended. </t>
-  </si>
-  <si>
     <t>STAT3 mutations have been reported in AML and may be present at initial diagnosis or acquired during leukemic transformation. (DOI: 10.1158/1078-0432.CCR-24-0066). They are found to most frequently coccur with SRSF2, TET2, ASXL1, and SETBP1 mutations.</t>
   </si>
   <si>
@@ -594,12 +550,6 @@
   </si>
   <si>
     <t>CEBPA mutations have been reported rarely in cases of CMML with an uncertain prognostic significance (DOI: 10.1182/bloodadvances.2024013648).</t>
-  </si>
-  <si>
-    <t>CMML and JMML have the highest reported frequencies of CBL mutation at approximately 13 to 15% of cases (DOI: 10.18632/oncotarget.3986). 
-Germline CBL mutations have been reported in JMML (DOI: 10.1038/ng.641).
-Please note that this assay cannot exclude the germline origin for the CBL c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended.
-Although rare, CBL mutations have been repoted in cases of MPN (DOI: 10.3324/haematol.2011.052605).</t>
   </si>
   <si>
     <t>CSF3R mutations have been reported in over 60% of CNL cases (WHO 5th Edition). CRF3R utations are less common in MPN/MDS  and reported in &lt;20% in MDS/MPN N. Coexisting ASXL1 mutation is associated with an adverse prognosis (WHO 5th edition).</t>
@@ -627,22 +577,6 @@
     <t>IKZF1 alteration has been reported very rarely in MF (DOI: 10.1182/blood.V128.22.1961.1961).</t>
   </si>
   <si>
-    <t>The presence of a pathogenic variant within MPL exon 10 is consistent with a myeloproliferative neoplasm. Activating MPL point mutations, particularly p.W515L/K, have been reported in 5-10% of cases of ET and PMF (WHO 5th Edition).
-Not hotspot:
-Please note that this variant is not the classic MPL hotspot mutation.
-Additional variants:
-While MPL mutations are considered driver events, mutations in other genes are found in over half of patients with MPN (WHO 5th Edition).
-Germline
-Please note that this assay cannot exclude the germline origin for the MPL c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended if clinically indicated.  Only use the following if it is a potentially germline variant with loss of function :MPL germline LoF variant – not previously described 
-This variant is not reported in the COSMIC database and is predicted to have an inactivating effect on the MPL gene. The variant allele frequency (VAF) of approximately 50% raises the possibility of a germline origin. Inactivating MPL variants have been described in individuals with congenital amegakaryocytic thrombocytopenia (CAMT; Germeshausen &amp; Ballmaier, Haematologica 2021;106(9):2439–2448). However, as CAMT is an autosomal recessive condition, affected individuals are typically homozygous or compound heterozygous for pathogenic variants in MPL.
-A constitutional (germline) sample has not been tested, and formal classification of this variant according to germline ACMG criteria has not been performed. Nonetheless, the current findings are most consistent with an incidental heterozygous germline variant, suggesting that the individual may be a carrier.
-In the absence of a family history of CAMT—a rare autosomal recessive condition—germline testing and cascade (carrier) testing in relatives are not routinely indicated. Further information is available from the laboratory upon request. Follow-up testing will not be performed without formal ACMG classification and discussion at the Genomics Tumour Advisory Board (GTAB).
-MPL germline variant described in CAMT
-Germline inactivating MPL variants have been described in individuals with congenital amegakaryocytic thrombocytopenia (CAMT; Germeshausen &amp; Ballmaier, Haematologica 2021;106(9):2439–2448). However, as CAMT is an autosomal recessive condition, affected individuals are typically homozygous or compound heterozygous for pathogenic variants in MPL.
-A constitutional (germline) sample has not been tested, and formal classification of this variant according to germline ACMG criteria has not been performed. Nonetheless, the current findings are most consistent with an incidental heterozygous germline variant, suggesting that the individual may be a carrier.
-In the absence of a family history of CAMT—a rare autosomal recessive condition—germline testing and cascade (carrier) testing in relatives are not routinely indicated. Further information is available from the laboratory upon request. Follow-up testing will not be performed without formal ACMG classification and discussion at the Genomics Tumour Advisory Board (GTAB).</t>
-  </si>
-  <si>
     <t>NF1 mutation has been reported very rarely in MPN cases (DOI: 10.1002/gcc.21960).</t>
   </si>
   <si>
@@ -652,23 +586,10 @@
     <t>NPM1 mutation is reported in a rare subset of CMML patients and is associated with an aggressive clinical course with rapid progression to acute leukaemia (ICC 2022). In the context of known CMML, detection of NPM1 is not used as a molecular defining feature of AML.</t>
   </si>
   <si>
-    <t>NRAS is commonly mutated in CMML and is associated with increased risk of transformation (WHO 5th Edition, CPSS-Mol).
-NRAS mutations are less common in MPN cases (WHO 5th Edition).
-NRAS mutations have been reported in MDS/MPN cases (WHO 5th Edition).
-JMML
-JMML is associated with mutations in RAS genes (NRAS 15 to 25%) or in regulators of the RAS pathway in more than 90% of cases (WHO 5th Edition). Please note that this assay cannot exclude the germline origin for the KRAS c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended.</t>
-  </si>
-  <si>
     <t>PHF6 mutations have been reported in CMML (DOI: 10.1182/blood-2024-206007).</t>
   </si>
   <si>
     <t>Truncating mutations in PPM1D have been reported in clonal haematopoiesis and myeloid neoplasms, and are particularly enriched in patients previously exposed to chemotherapy (DOI: 10.1182/blood-2018-05-850339).</t>
-  </si>
-  <si>
-    <t>JMML
-PTPN11 mutation is reported in 35-40% of JMML cases (WHO 5th Edition). Please note that this assay cannot exclude the germline origin for the PTPN11 c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended.
-Unknown diagnosis
-PTPN11 mutations have been reported in CMML, CNL and MDS/MPN (WHO 5th Edition).</t>
   </si>
   <si>
     <t>PRPF8 mutations have been reported infrequently in myeloid malignancies (DOI: 10.1038/leu.2014.144).</t>
@@ -1261,12 +1182,6 @@
     <t>Mutations or rearrangements in CSF1R have been implicated in a subset of histiocytic neoplasms and are more commonly associated with non-LCH histiocytoses (DOI: 10.1182/blood-2018-99-114248).</t>
   </si>
   <si>
-    <t>Del(13q) occurs in 50-60% of CLL patients and removes the DLEU2-miR-15-16 cluster (WHO 5th Edition).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focal copy number loss of the RB1 gene was detected. </t>
-  </si>
-  <si>
     <t>SMZL</t>
   </si>
   <si>
@@ -1399,12 +1314,6 @@
 This report includes only copy number aberrations pertinent to CLL (tier 1 or tier 2). CNV analysis for chronic lymphocytic leukaemia (CLL) includes chromosome 11, 12, 13, and the short arm of chromosome 17 (17p).</t>
   </si>
   <si>
-    <t>This report includes only copy number aberrations pertinent to CLL (tier 1 or tier 2). CNV analysis for chronic lymphocytic leukaemia (CLL) includes chromosome 11, 12, 13, and the short arm of chromosome 17 (17p).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLL reporting caveat (applied to all cases with a CNV) </t>
-  </si>
-  <si>
     <t>WT1 mutation is reported in approximately 15% of AML cases (DOI: 10.1182/blood-2022-166323). It has been associated with an increased risk of post transplant relapse in patients with intermediate risk genetics (DOI: 10.1182/blood-2022-166323).</t>
   </si>
   <si>
@@ -1414,9 +1323,6 @@
     <t>Please note the quantity of DNA obtained from this sample did not meet the quality criteria for NGS testing. Please send a repeat sample, if possible.</t>
   </si>
   <si>
-    <t>Copy number analysis has not been performed, as it has only been validated for samples with ≥40% neoplastic content.</t>
-  </si>
-  <si>
     <t>&lt;40% tumour content CNV</t>
   </si>
   <si>
@@ -1442,9 +1348,6 @@
   </si>
   <si>
     <t>CNV analysis by NGS was not performed for this sample due to high genome wide disruption, which prevented reliable assessment of copy number variation.</t>
-  </si>
-  <si>
-    <t>The neoplastic cell content of this sample is not available. The presence of low-level variants cannot be excluded. This assay has been validated to detect small variants present at ≥1% mutant DNA in a background of wild-type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
   </si>
   <si>
     <t>STAT5B variants are reported in a number of T lymphoid malignancies (WHO 5th Edition).
@@ -1455,21 +1358,10 @@
     <t>NGS negative tumour content unknown</t>
   </si>
   <si>
-    <t>Please review the tumour content of the sample for interpretation of this result. Low tumour content reduces the sensitivity of NGS and it may result in false negative findings. This assay has been validated to detect as little as 1% mutant DNA in a background of wild type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
-  </si>
-  <si>
     <t>Del(13q) DLEU2/miR15</t>
   </si>
   <si>
-    <t>Del(17p) (TP53 deletion)
-note: del(17p) is mostly accompanied by TP53 mutations, and sole del(17p) is infrequent, while sole TP53 mutations are more commonly found (ERIC 2024)
-If TP53 mutation is also detected</t>
-  </si>
-  <si>
     <t>Del(11q) (ATM)</t>
-  </si>
-  <si>
-    <t>RB1 copy number loss (focal, to be used in absence of miR 15 loss)</t>
   </si>
   <si>
     <t>VAV1 variants have been reported in angioimmunoblastic T-cell lymphoma (AITL) and nodal PTCL with T-follicular helper (Tfh) phenotype (PTCL-Tfh) (DOI: 10.1182/blood.2020006513).</t>
@@ -1527,9 +1419,6 @@
   </si>
   <si>
     <t>DLEU2/miR15 del focal</t>
-  </si>
-  <si>
-    <t>CNV analysis detected copy number loss of chromosome 13q14 containing the DLEU2¬-miR¬-15¬-16 cluster. This is frequently reported in CLL (WHO 5th Edition).</t>
   </si>
   <si>
     <t>Oncogene, tumour suppressor</t>
@@ -1998,11 +1887,6 @@
   </si>
   <si>
     <t>GNB1 is recurrently mutated in MDS, and mutations are included in the IPSS-M (DOI: 10.1056/EVIDoa2200008).</t>
-  </si>
-  <si>
-    <t>NPM1 mutations are reported in MDS, please refer to the IPSS-M for prognostic indications (DOI: 10.1056/EVIDoa2200008).
-***Note: According to the WHO 5th Edition, the presence of an NPM1 mutation is considered an AML-defining genetic abnormality irrespective of blast percentage. Cases with morphological features overlapping with myelodysplastic neoplasms or myelodysplastic/myeloproliferative neoplasms (including CMML) should be classified as AML with NPM1 mutation when the mutation is detected at presentation.
-In contrast, under the ICC 2022, a diagnosis of AML with mutated NPM1 requires ≥10% blasts.***</t>
   </si>
   <si>
     <t>SETBP1 mutations are reported in MDS, please refer to the IPSS-M for prognostic indications (DOI: 10.1056/EVIDoa2200008).  
@@ -2138,14 +2022,6 @@
 TET2 comutation has been reported in AML with CBFB::MYH11, AML with KMT2A rearrangement and frequently in AML with NPM1 mutation (WHO 5th Edition).</t>
   </si>
   <si>
-    <t>CNV analysis detected copy number loss of chromosome 13q14 containing the DLEU2-miR-15-16 cluster. This is frequently reported in CLL (WHO 5th Edition).</t>
-  </si>
-  <si>
-    <t>Del(17p) occurs in 4 to 8% of early stage CLL, 5 to 8% at the start of first-line therapy, and 40–50% in relapsed/refractory CLL.
-Del(17p) and/or TP53 mutation have the strongest impact on the prognosis and the prediction of therapeutic outcome in CLL. They are associated with significantly worse progression-free survival (PFS) and overall survival (OS), both without treatment and with chemoimmunotherapy (CIT). However, their negative impact is less pronounced with targeted therapies like BTK and BCL2 inhibitors, which offer longer response durations and improved PFS and OS compared to CIT (WHO 5th ed.).
-The prognostic impact of single hit TP53 abnormalities (e.g., isolated del(17p) or TP53 mutation) with targeted therapies is currently unclear. Conversely, multi-hit TP53 aberrations (concomitant TP53 mutation and del(17p)) consistently correlates with poorer outcomes. (ERIC, 2024).</t>
-  </si>
-  <si>
     <t>Del(17p) (TP53 deletion)
 note: del(17p) is mostly accompanied by TP53 mutations, and sole del(17p) is infrequent, while sole TP53 mutations are more commonly found (ERIC 2024)</t>
   </si>
@@ -2210,6 +2086,48 @@
   <si>
     <t>***check that cyto have a sample***
 As the percentage neoplastic cell content in this sample is &lt;40% by immunophenotyping, we cannot exclude the presence of copy number variants. Targeted FISH testing for TP53/ATM has been activated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If suspected germline: 
+Germline RUNX1 mutated AML is encompassed by the WHO 5th Edition disease category of Myeloid neoplasms with germline predisposition and pre-existing platelet disorders. Heterozygous deleterious variants confer lifelong thrombocytopenia with variable degrees of platelet dysfunction and risk for myeloid malignancies (also referred to as familial platelet disorder). 
+AML patients with germline RUNX1 mutations have shown enrichment for somatic mutations affecting the second RUNX1 allele and GATA2 (DOI: 10.1182/bloodadvances.2019000901).
+Please note that this assay cannot exclude the germline origin for the RUNX1 c.xxx p.(xxx) variant. Identification of a germline predisposition may have implications for patient management including donor selection for allogeneic transplantation. Referral to clinical genetics service for family history and further assessment is recommended. </t>
+  </si>
+  <si>
+    <t>*Current agreement is to not report potential germline MPL mutations*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germline:
+Myeloid neoplasms with germline ETV6 mutation is a WHO and ICC disease category (WHO 5th edition and ICC 2022).
+Please note that this assay cannot exclude the germline origin for the ETV6 c.xxx p.(xxx) variant. ETV6 germline variants are typically associated with lifelong thrombocytopenia and an increased risk of haematological malignancies. Identification of a germline predisposition may have implications for patient management including donor selection for allogeneic transplantation.  Referral to clinical genetics service for family history and further assessment is recommended. </t>
+  </si>
+  <si>
+    <t>Germline CBL mutations have been reported in JMML (DOI: 10.1038/ng.641).
+Please note that this assay cannot exclude the germline origin for the CBL c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended.</t>
+  </si>
+  <si>
+    <t>If suspected germline:
+Germline CEBPA mutations are estimated to occur in 10% of all CEBPA mutated AML cases. Please note that this assay cannot exclude the germline origin for the CEBPA variant. Identification of a germline predisposition may have implications for patient management including donor selection for allogeneic transplantation. Referral to clinical genetics service for family history and further assessment is recommended. 
+Biallelic with potential germline:
+Among cases with biallelic CEBPA mutations, approximately 5 to 10% have a germline N terminal mutation (WHO 5th edition). Please note that this assay cannot exclude the germline origin for the CEBPA variants. Identification of a germline predisposition may have implications for patient management including donor selection for allogeneic transplantation. Referral to clinical genetics service for family history and further assessment is recommended.
+RECCOMENDED READING: DOI 10.1038/s41375-024-02140-x</t>
+  </si>
+  <si>
+    <t>NPM1 mutations are reported in MDS, please refer to the IPSS-M for prognostic indications (DOI: 10.1056/EVIDoa2200008).
+***Note: According to the WHO 5th Edition, the presence of an NPM1 mutation is considered an AML-defining genetic abnormality irrespective of blast percentage. Cases with morphological features overlapping with myelodysplastic neoplasms or myelodysplastic/myeloproliferative neoplasms (including CMML) should be classified as AML with NPM1 mutation when the mutation is detected at presentation.
+In contrast, under the ICC 2022, a diagnosis of AML with mutated NPM1 requires greater than or equal to 10% blasts.***</t>
+  </si>
+  <si>
+    <t>Please review the tumour content of the sample for interpretation of this result. Low tumour content reduces the sensitivity of NGS and it may result in false negative findings. This assay has been validated to detect as little as 1% mutant DNA in a background of wild type DNA. Copy number analysis has not been performed as it has only been validated for samples with greater than or equal to 40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>The neoplastic cell content of this sample is not available. The presence of low-level variants cannot be excluded. This assay has been validated to detect small variants present at greater than or equal to 1% mutant DNA in a background of wild-type DNA. Copy number analysis has not been performed as it has only been validated for samples with greater than or equal to 40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>Copy number analysis has not been performed, as it has only been validated for samples with greater than or equal to 40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>CNV analysis detected multiple copy number gains and/or copy number losses, suggestive of genomic complexity. Genomic complexity is an independent negative prognostic marker in CLL, particularly for greater than or equal to  5 copy number aberrations in TP53 wildtype cases (WHO 5th ed, ERIC 2022).</t>
   </si>
 </sst>
 </file>
@@ -2693,7 +2611,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C27" dT="2025-10-24T14:51:55.67" personId="{E177F675-2BF7-4D34-B125-6F3DDBFD449B}" id="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
+  <threadedComment ref="C11" dT="2025-10-24T14:51:55.67" personId="{E177F675-2BF7-4D34-B125-6F3DDBFD449B}" id="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
     <text>Incorrect in WHO - PTEN is on 10q</text>
   </threadedComment>
 </ThreadedComments>
@@ -2718,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105.75" x14ac:dyDescent="0.25">
@@ -2726,10 +2644,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C2" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2738,10 +2656,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2749,10 +2667,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2760,505 +2678,505 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="C8" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="C12" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="106.5" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="C13" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
       <c r="C14" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C16" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="333" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="C17" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="C19" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="C21" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="C22" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="C24" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="285" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="C29" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="345" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="C36" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C39" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="C41" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="C42" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="C45" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C47" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="C48" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="C49" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C50" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -3287,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3295,10 +3213,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3306,10 +3224,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3317,7 +3235,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3325,492 +3243,492 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3836,10 +3754,10 @@
     </row>
     <row r="2" spans="1:16384" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:16384" ht="90" x14ac:dyDescent="0.2">
@@ -3847,23 +3765,23 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16384" ht="409.5" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16384" ht="180" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16384" ht="120" x14ac:dyDescent="0.2">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16384" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>152</v>
+        <v>516</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4"/>
@@ -20250,66 +20168,66 @@
     </row>
     <row r="6" spans="1:16384" ht="270" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16384" ht="180" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16384" ht="105" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>123</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8" spans="1:16384" ht="120" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:16384" ht="120" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16384" ht="409.5" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16384" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16384" ht="150" x14ac:dyDescent="0.2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16384" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16384" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16384" ht="135" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16384" ht="90" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16384" ht="360" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="B13" s="4" t="s">
-        <v>133</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -20336,7 +20254,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20344,77 +20262,77 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="C4" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="C8" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -20441,7 +20359,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -20449,10 +20367,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -20460,10 +20378,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -20471,10 +20389,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -20482,285 +20400,285 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C10" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="C11" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C12" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C13" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C15" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="C16" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C17" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C18" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="C19" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="C20" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C21" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="C22" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="C23" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="C24" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="C25" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="C26" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C28" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="C29" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="C30" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -20784,175 +20702,175 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="C4" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="C9" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="C10" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="C11" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="C12" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="C13" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="C14" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C15" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="C16" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -20977,7 +20895,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -20985,10 +20903,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -20996,10 +20914,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C3" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -21008,65 +20926,65 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C4" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="C5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="C6" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C9" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -21094,7 +21012,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -21102,118 +21020,118 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="C4" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="C7" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="C9" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="C10" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="C11" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="C12" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -21239,7 +21157,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -21247,108 +21165,108 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C3" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C4" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C8" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C11" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -21371,130 +21289,130 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>358</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>355</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>345</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -21521,82 +21439,82 @@
     </row>
     <row r="2" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -21623,7 +21541,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -21631,10 +21549,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -21642,10 +21560,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -21653,10 +21571,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -21664,522 +21582,522 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="225" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>505</v>
+        <v>479</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -22189,7 +22107,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9F24A3-EA82-4A17-B915-0BA86DD79F59}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -22199,299 +22117,123 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="A2" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A3" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A4" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B7" s="17" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="225" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>45</v>
+      <c r="C7" s="15" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="B18" s="17" t="s">
+      <c r="A8" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C8" s="15" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>300</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C9" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="C19" s="15" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="B20" s="17" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="B11" s="17" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>306</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A26" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
-        <v>321</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -22501,188 +22243,6 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD11A77-8F37-4406-B8E5-36CB8A85C790}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="44.33203125" customWidth="1"/>
-    <col min="2" max="2" width="73.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="210" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB04A814-2B61-4507-B2B6-E5CF9076F40B}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -22693,222 +22253,222 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>525</v>
+        <v>497</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="B2" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>538</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>539</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>540</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B8" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>531</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>535</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="285" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>523</v>
+        <v>495</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>536</v>
+        <v>508</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>537</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>522</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -22949,7 +22509,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -22957,10 +22517,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -22968,10 +22528,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>466</v>
+        <v>441</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="75" x14ac:dyDescent="0.2">
@@ -22979,10 +22539,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -22990,506 +22550,506 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>471</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>475</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>478</v>
+        <v>453</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>479</v>
+        <v>454</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="75" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>485</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>488</v>
+        <v>463</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>487</v>
+        <v>462</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="135" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>490</v>
+        <v>465</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>491</v>
+        <v>466</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>494</v>
+        <v>469</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -23514,62 +23074,62 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -23595,7 +23155,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -23604,7 +23164,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -23612,10 +23172,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -23623,10 +23183,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -23634,474 +23194,474 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>464</v>
+        <v>439</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>461</v>
+        <v>436</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -24127,7 +23687,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -24136,7 +23696,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -24145,7 +23705,7 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -24153,10 +23713,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -24165,429 +23725,429 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -24613,7 +24173,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -24622,7 +24182,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -24630,10 +24190,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>465</v>
+        <v>440</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -24642,7 +24202,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -24651,407 +24211,407 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -25077,7 +24637,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -25086,7 +24646,7 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -25095,7 +24655,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -25103,7 +24663,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -25111,413 +24671,413 @@
         <v>7</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>489</v>
+        <v>464</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -25543,7 +25103,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -25551,10 +25111,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -25562,10 +25122,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -25573,7 +25133,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -25581,492 +25141,492 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/NGS_comments_automation_further_review.xlsx
+++ b/NGS_comments_automation_further_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677BE400-22EC-44C8-8652-40C40ED94734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA217782-B8CD-4D63-9781-63ABED7EF415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30570" yWindow="-1080" windowWidth="25980" windowHeight="14790" firstSheet="13" activeTab="20" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="29445" yWindow="-375" windowWidth="25980" windowHeight="14790" firstSheet="13" activeTab="19" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="518">
   <si>
     <t>Gene</t>
   </si>
@@ -151,9 +151,6 @@
   </si>
   <si>
     <t>&lt;10% neoplastic cells (CLL)</t>
-  </si>
-  <si>
-    <t>Please note that clonal B cells with a CLL/SLL phenotype represent only xx% of the total nucleated cells according to flow cytometry.  Therefore, we cannot exclude the presence of low-level variants in this sample.</t>
   </si>
   <si>
     <t xml:space="preserve">Please note the coverage was suboptimal for some regions analysed within [list genes] which may affect the sensitivity of the assay for detection of variants close to the limit of detection. </t>
@@ -1071,12 +1068,6 @@
     <t xml:space="preserve">TENT5C is recurrently mutated, or genetically deleted, in 20% of multiple myeloma (MM) patients (DOI: 10.1182/blood-2025-1027). </t>
   </si>
   <si>
-    <t>Disease</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
     <t xml:space="preserve">TP53 variants are frequently reported in B-NHL with a more aggressive disease course (DOI: 10.1002/ijc.30838).
 MCL
 TP53 is recurrently altered in mantle cell lymphoma and often associated with disease progression (WHO 5th Edition).
@@ -1182,54 +1173,36 @@
     <t>Mutations or rearrangements in CSF1R have been implicated in a subset of histiocytic neoplasms and are more commonly associated with non-LCH histiocytoses (DOI: 10.1182/blood-2018-99-114248).</t>
   </si>
   <si>
-    <t>SMZL</t>
-  </si>
-  <si>
     <t>7q-</t>
   </si>
   <si>
     <t xml:space="preserve">Deletion of 7q31-32 is found in around 30% of SMZL cases and rarely reported in other types of B-cell lymphoma/leukemia (WHO 5th Edition). </t>
   </si>
   <si>
-    <t>MZL (all types)</t>
-  </si>
-  <si>
     <t>trisomy 3, 18</t>
   </si>
   <si>
     <t>Co-occurrence of trisomies of chromosomes 3 and 18 is observed in about 25% of cases of across the three marginal zone lymphoma entities (WHO 5th Edition).</t>
   </si>
   <si>
-    <t>WM</t>
-  </si>
-  <si>
     <t>6q-</t>
   </si>
   <si>
     <t>Clonal deletions of chromosome 6, targeting regions 6q21-q25, are found in 40–50% of patients with WM and appear to be exclusively associated with CXCR4 mutations in treatment-naïve patients (WHO 5th Edition).</t>
   </si>
   <si>
-    <t>FL</t>
-  </si>
-  <si>
     <t>1p</t>
   </si>
   <si>
     <t>Deletions of chromosome 1p have been reported in FL (WHO 5th Edition).</t>
   </si>
   <si>
-    <t>Atypical CLL</t>
-  </si>
-  <si>
     <t>trisomy 12</t>
   </si>
   <si>
     <t>Trisomy 12 may support a diagnosis of atypical CLL in the correct clinical context (WHO 5th Edition).</t>
   </si>
   <si>
-    <t>T-PLL</t>
-  </si>
-  <si>
     <t>11q del</t>
   </si>
   <si>
@@ -1252,9 +1225,6 @@
   </si>
   <si>
     <t>CNV analysis showed a complex profile. Deletions in 12p13 and 22q , gains in 8q24 (MYC) and abnormalities of chromosomes 5p, 6, and 17  have also been described in T-PLL (WHO 5th edition)</t>
-  </si>
-  <si>
-    <t>PTCL NOS</t>
   </si>
   <si>
     <t>17p-, 9p- (CDKN2A), 10p- (PTEN)</t>
@@ -2128,6 +2098,21 @@
   </si>
   <si>
     <t>CNV analysis detected multiple copy number gains and/or copy number losses, suggestive of genomic complexity. Genomic complexity is an independent negative prognostic marker in CLL, particularly for greater than or equal to  5 copy number aberrations in TP53 wildtype cases (WHO 5th ed, ERIC 2022).</t>
+  </si>
+  <si>
+    <t>Please note that clonal B cells with a CLL/SLL phenotype represent only xx% of the total nucleated cells according to flow cytometry. Therefore, we cannot exclude the presence of low-level variants in this sample.</t>
+  </si>
+  <si>
+    <t>Copy number analysis has not been performed as it has only been validated for samples with greater than or equal to 40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>&lt;40%</t>
+  </si>
+  <si>
+    <t>Any, below threshold finding</t>
+  </si>
+  <si>
+    <t>This finding is below the validated threshold for this assay, which may be due to low neoplastic cell content or the presence of subclonal populations. Please confirm by an orthoganol method if clinically indicated.</t>
   </si>
 </sst>
 </file>
@@ -2204,7 +2189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2253,9 +2238,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2636,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105.75" x14ac:dyDescent="0.25">
@@ -2644,10 +2626,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2656,10 +2638,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2667,10 +2649,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2678,505 +2660,505 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C10" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C12" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="106.5" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C13" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C14" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C16" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="333" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C17" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C19" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C20" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C21" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C22" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C24" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="285" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="C29" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="345" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C36" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C39" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C41" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C42" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C44" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C45" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C46" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C47" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C48" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C49" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C50" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -3205,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3213,10 +3195,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3224,10 +3206,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3235,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3243,492 +3225,492 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3754,10 +3736,10 @@
     </row>
     <row r="2" spans="1:16384" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:16384" ht="90" x14ac:dyDescent="0.2">
@@ -3765,23 +3747,23 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:16384" ht="180" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:16384" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4"/>
@@ -20168,66 +20150,66 @@
     </row>
     <row r="6" spans="1:16384" ht="270" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:16384" ht="105" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" spans="1:16384" ht="120" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:16384" ht="120" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:16384" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="1:16384" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" spans="1:16384" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="1:16384" ht="135" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -20254,7 +20236,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20262,77 +20244,77 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C4" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -20359,7 +20341,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -20367,10 +20349,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -20378,10 +20360,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -20389,10 +20371,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -20400,285 +20382,285 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C10" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C12" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C13" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C15" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C16" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C17" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C18" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C19" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C20" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C21" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C22" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C23" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C24" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C25" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C26" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C28" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C29" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C30" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -20702,175 +20684,175 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C10" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C11" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C12" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C13" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C14" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C16" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -20895,7 +20877,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -20903,10 +20885,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -20914,10 +20896,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -20926,65 +20908,65 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C6" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C9" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -21012,7 +20994,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -21020,118 +21002,118 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C4" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C6" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C7" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C9" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C10" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C11" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C12" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -21157,7 +21139,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -21165,108 +21147,108 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C4" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -21297,10 +21279,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -21308,7 +21290,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -21316,15 +21298,15 @@
         <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -21332,87 +21314,87 @@
         <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>342</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>341</v>
+        <v>332</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -21439,82 +21421,82 @@
     </row>
     <row r="2" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -21541,7 +21523,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -21549,10 +21531,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -21560,10 +21542,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -21571,10 +21553,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -21582,522 +21564,522 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="225" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -22107,7 +22089,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9F24A3-EA82-4A17-B915-0BA86DD79F59}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -22117,10 +22099,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>246</v>
+        <v>487</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>492</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>14</v>
@@ -22128,112 +22110,134 @@
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>280</v>
+        <v>490</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>283</v>
+        <v>490</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
-        <v>286</v>
+        <v>490</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
-        <v>289</v>
+        <v>490</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A8" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="B6" s="17" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A10" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>293</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C10" s="15" t="s">
         <v>294</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
-        <v>304</v>
+        <v>490</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>306</v>
+        <v>296</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A13" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -22253,10 +22257,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>14</v>
@@ -22264,211 +22268,211 @@
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="B2" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B8" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="285" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -22509,7 +22513,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -22517,10 +22521,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -22528,10 +22532,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="75" x14ac:dyDescent="0.2">
@@ -22539,10 +22543,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -22550,506 +22554,506 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="75" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="135" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -23074,62 +23078,62 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -23155,7 +23159,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -23164,7 +23168,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -23172,10 +23176,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -23183,10 +23187,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -23194,474 +23198,474 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -23687,7 +23691,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -23696,7 +23700,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -23705,7 +23709,7 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -23713,10 +23717,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -23725,429 +23729,429 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -24173,7 +24177,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -24182,7 +24186,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -24190,10 +24194,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -24202,7 +24206,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -24211,407 +24215,407 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -24637,7 +24641,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -24646,7 +24650,7 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -24655,7 +24659,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -24663,7 +24667,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -24671,413 +24675,413 @@
         <v>7</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -25103,7 +25107,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -25111,10 +25115,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -25122,10 +25126,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -25133,7 +25137,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -25141,492 +25145,492 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
